--- a/etl/data/source_table_map.xlsx
+++ b/etl/data/source_table_map.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Files" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$1:$M$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source x Table'!$A$1:$F$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tables'!$A$1:$F$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source x Table'!$A$1:$F$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tables'!$A$1:$F$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Input Files'!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -543,8 +543,8 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py
-cargo_operational_requirement.py</t>
+          <t>chemical/master_loader.py
+chemical/cargo_operational_requirement.py</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -648,9 +648,9 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>dot_hmt_extract.py
-dot_hazmat_symbol_loader.py
-cargo_dot_hazad_loader.py</t>
+          <t>chemical/dot_hmt_extract.py
+chemical/dot_hazmat_symbol_loader.py
+chemical/cargo_dot_hazad_loader.py</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>compatibility_exception_loader.py</t>
+          <t>chemical/compatibility_exception_loader.py</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -752,21 +752,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sittig_handbook.py</t>
+          <t>chemical/sittig_handbook.py</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>cargo_chemical
 cargo_property_values
-cargo_synonym</t>
+cargo_synonym
+synonyms</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>34640</v>
+        <v>37304</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -857,8 +858,8 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>proceduretemplate.py
-verwey_cleaning.py</t>
+          <t>chemical/proceduretemplate.py
+chemical/verwey_cleaning.py</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -873,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>713852</v>
+        <v>819486</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -897,30 +898,642 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Drew Ameroid Tank Cleaning Guide.xlsx</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>chemical/drew_ameroid.py</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_process
+procedure_template_steps
+procedure_templates</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3789</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Miracle Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Miracle Tank Cleaning Guide.xlsx</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>chemical/master_loader.py</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>cargo_chemical
+cargo_property_values
+cargo_synonym
+cargo_un_number
+cleaning_process
+cleaning_process_step
+synonyms</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24866</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Odfjell Compatibility Chart</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999 .xlsx
+cargo_chemicals_groupData.csv</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>chemical/cargo_compatibility.py
+chemical/reactive_group.py
+chemical/link_cargo_reactive_groups.py</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Stolt commodity table / Produkt info</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Union Carbide Product Stowage Guide</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Lars Stole Birkeland - Chemical Cargo specifications - 2002.xlsx - CGOSPEC.csv</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>chemical/master_loader.py</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>cargo_chemical
+cargo_property_values
+cargo_synonym
+cargo_un_number
+synonyms</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11137</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INTERTANKO Cargo Tank Cleanliness Standards</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rev 1 2017</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Manual Entry</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unknown - Products CHEM - 1996</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Products CHEM - 1996.XLS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>chemical/master_loader.py</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>cargo_chemical
+cargo_property_values</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO.xlsx</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>chemical/master_loader.py</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>cargo_reactive_group
+compatibility
+master_cargo_chemical_group_details
+reactive_groups</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999 .xlsx</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>chemical/cargo_compatibility.py</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed.csv</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>chemical/master_loader.py</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>cargo_chemical
+cargo_hazard_data
+cargo_property_values
+cargo_synonym
+cargo_un_number
+synonyms</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5742</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cargo Library 2 DOT_hazardous_materials</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>cargo_dot_hazad
+cargo_hazard_data</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3714</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>PDF Book</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Dr Verweys Tank Cleaning Guide Pdf Book - Cargo details.csv
 Dr Verweys Tank Cleaning Guide Pdf Book Procdure Template.csv
 Dr Verweys Tank Cleaning Guide Pdf Book  _from-to procedure.csv</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>verwey_pdf_book.py
-verwey_pdf_book_procedures.py
-verwey_pdf_book_families.py
-verwey_pdf_book_matrix.py</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>chemical/verwey_pdf_book.py
+chemical/verwey_pdf_book_procedures.py
+chemical/verwey_pdf_book_families.py
+chemical/verwey_pdf_book_matrix.py</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>cargo_chemical
 cargo_family_group
@@ -929,775 +1542,378 @@
 cleaning_process
 procedure_template_instruction
 procedure_template_steps
-procedure_templates</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>193221</v>
-      </c>
-      <c r="I9" t="n">
+procedure_templates
+synonyms</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>191546</v>
+      </c>
+      <c r="I22" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L22" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M22" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="23">
+      <c r="A23" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crude Oil Basic Properties</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>crude_oil
+crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>547</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Crude Oil Assay and Operational Properties</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>crude_oil
+crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6136</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_process
+crude_oil
+crude_oil_property_values
+crude_oil_synonym
+procedure_note
+procedure_template_instruction
+procedure_template_steps
+procedure_templates
+synonyms</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Drew Ameroid Tank Cleaning Guide.xlsx</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>drew_ameroid.py</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H25" t="n">
+        <v>1597</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>27</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HM 50</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>cleaning_process
+crude_oil
+crude_oil_property_values
 procedure_template_steps
 procedure_templates</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>683</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>28</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>White Oil</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_process
+crude_oil
+crude_oil_compatibility
+crude_oil_synonym
+procedure_template_steps
+procedure_templates
+synonyms</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>593</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_process
+crude_oil
+crude_oil_property_values
+procedure_template_steps
+procedure_templates</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>554</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_process
+crude_oil
+crude_oil_compatibility
+crude_oil_property_values
+procedure_template_steps
+procedure_templates</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>200</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VAPDENS.XLSX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>3099</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Miracle Tank Cleaning Guide</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Miracle Tank Cleaning Guide.xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>master_loader.py</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>cargo_chemical
-cargo_property_values
-cargo_synonym
-cargo_un_number
-cleaning_process
-cleaning_process_step</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>19303</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Odfjell Compatibility Chart</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999 .xlsx
-cargo_chemicals_groupData.csv</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>cargo_compatibility.py
-reactive_group.py
-link_cargo_reactive_groups.py</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Stolt commodity table / Produkt info</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Union Carbide Product Stowage Guide</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Lars Stole Birkeland - Chemical Cargo specifications - 2002.xlsx - CGOSPEC.csv</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>master_loader.py</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>cargo_chemical
-cargo_property_values
-cargo_synonym
-cargo_un_number</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8571</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>INTERTANKO Cargo Tank Cleanliness Standards</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rev 1 2017</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Manual Entry</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 4 Odfjell - Compatibility Chart and Notes Reactive Cargoes - 1999 .xlsx</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>cargo_compatibility.py</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>master_loader.py</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>cargo_reactive_group
-compatibility
-master_cargo_chemical_group_details
-reactive_groups</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2882</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cargo Library 2 DOT_hazardous_materials</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>cargo_dot_hazad
-cargo_hazard_data</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3695</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7th 1990</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed.csv</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>master_loader.py</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>cargo_chemical
-cargo_hazard_data
-cargo_property_values
-cargo_synonym
-cargo_un_number</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4660</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Unknown - Products CHEM - 1996</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Products CHEM - 1996.XLS</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>master_loader.py</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>cargo_chemical
-cargo_property_values</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>909</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Crude Oil Basic Properties</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>crude_oil
-crude_oil_property_values</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>547</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Crude Oil Assay and Operational Properties</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>crude_oil
-crude_oil_property_values</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>6136</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1708,13 +1924,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1860,7 +2076,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
@@ -1930,49 +2146,49 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>ORIGIN ONLY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide</t>
+          <t>Sittigs Handbook of Toxic &amp; Hazardous Chemicals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cleaning_process_step</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>cleaning_process_step.cleaning_process_id -&gt; cleaning_process.id -&gt; cleaning_process.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>595617</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10">
@@ -1986,21 +2202,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cleaning_process</t>
+          <t>cleaning_process_step</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cleaning_process.source_id</t>
+          <t>cleaning_process_step.cleaning_process_id -&gt; cleaning_process.id -&gt; cleaning_process.source_id</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>118027</v>
+        <v>683770</v>
       </c>
     </row>
     <row r="11">
@@ -2014,21 +2230,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>procedure_template_steps</t>
+          <t>cleaning_process</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+          <t>cleaning_process.source_id</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>171</v>
+        <v>135508</v>
       </c>
     </row>
     <row r="12">
@@ -2042,35 +2258,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>procedure_templates</t>
+          <t>procedure_template_steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>procedure_templates.source_id</t>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Dr Verweys Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cleaning_process</t>
+          <t>procedure_templates</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2080,11 +2296,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cleaning_process.source_id</t>
+          <t>procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>184468</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2093,12 +2309,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cargo_property_values</t>
+          <t>cleaning_process</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2108,11 +2324,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>cargo_property_values.source_id</t>
+          <t>cleaning_process.source_id</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5760</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2337,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2140,7 +2356,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1158</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
@@ -2149,40 +2365,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>procedure_template_instruction</t>
+          <t>procedure_templates</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>procedure_template_instruction.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+          <t>procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>567</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>cargo_synonym</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2192,81 +2408,81 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>cargo_synonym.source_id</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>555</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cargo_family_group</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>ORIGIN ONLY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cargo_family_group.source_id</t>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>431</v>
+        <v>5563</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>procedure_templates</t>
+          <t>cleaning_process_step</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>procedure_templates.source_id</t>
+          <t>cleaning_process_step.cleaning_process_id -&gt; cleaning_process.id -&gt; cleaning_process.source_id</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>279</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cargo_synonym</t>
+          <t>cargo_property_values</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2276,11 +2492,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cargo_synonym.source_id</t>
+          <t>cargo_property_values.source_id</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="21">
@@ -2289,7 +2505,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2308,7 +2524,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2969</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="22">
@@ -2317,26 +2533,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>procedure_template_steps</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23">
@@ -2345,12 +2561,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Drew Ameroid Tank Cleaning Guide (TCG)</t>
+          <t>Miracle Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>procedure_templates</t>
+          <t>cargo_un_number</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2360,25 +2576,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>procedure_templates.source_id</t>
+          <t>cargo_un_number.source_id</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cargo_synonym</t>
+          <t>cargo_property_values</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2388,81 +2604,81 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cargo_synonym.source_id</t>
+          <t>cargo_property_values.source_id</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6428</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cleaning_process_step</t>
+          <t>cargo_synonym</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cleaning_process_step.cleaning_process_id -&gt; cleaning_process.id -&gt; cleaning_process.source_id</t>
+          <t>cargo_synonym.source_id</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5250</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cargo_property_values</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>ORIGIN ONLY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cargo_property_values.source_id</t>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5230</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cleaning_process</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2472,25 +2688,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>cleaning_process.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1248</v>
+        <v>968</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>cargo_un_number</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2500,25 +2716,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>cargo_un_number.source_id</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>791</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Miracle Tank Cleaning Guide</t>
+          <t>Unknown - Products CHEM - 1996</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cargo_un_number</t>
+          <t>cargo_property_values</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2528,25 +2744,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cargo_un_number.source_id</t>
+          <t>cargo_property_values.source_id</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>356</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
+          <t>Unknown - Products CHEM - 1996</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cargo_property_values</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2556,25 +2772,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>cargo_property_values.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4694</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>cargo_synonym</t>
+          <t>cargo_reactive_group</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2584,53 +2800,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>cargo_synonym.source_id</t>
+          <t>cargo_reactive_group.source_id</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2661</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>master_cargo_chemical_group_details</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>master_cargo_chemical_group_details.group_code -&gt; reactive_groups.group_code -&gt; reactive_groups.source_id</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>968</v>
+        <v>698</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lars Stole Birkeland — Chemical Cargo specifications - 2002</t>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cargo_un_number</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2640,16 +2856,16 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cargo_un_number.source_id</t>
+          <t>compatibility.source_id</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>248</v>
+        <v>561</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2658,7 +2874,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cargo_reactive_group</t>
+          <t>reactive_groups</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2668,53 +2884,53 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cargo_reactive_group.source_id</t>
+          <t>reactive_groups.source_id</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1586</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>master_cargo_chemical_group_details</t>
+          <t>cargo_property_values</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>master_cargo_chemical_group_details.group_code -&gt; reactive_groups.group_code -&gt; reactive_groups.source_id</t>
+          <t>cargo_property_values.source_id</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>698</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>compatibility</t>
+          <t>cargo_synonym</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2724,53 +2940,53 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>compatibility.source_id</t>
+          <t>cargo_synonym.source_id</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>561</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>reactive_groups</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>ORIGIN ONLY</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>reactive_groups.source_id</t>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>37</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cargo Library 2 DOT_hazardous_materials</t>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cargo_dot_hazad</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2780,20 +2996,20 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>cargo_dot_hazad.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3594</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cargo Library 2 DOT_hazardous_materials</t>
+          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2812,7 +3028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>101</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40">
@@ -2826,7 +3042,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cargo_property_values</t>
+          <t>cargo_un_number</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2836,25 +3052,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>cargo_property_values.source_id</t>
+          <t>cargo_un_number.source_id</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
+          <t>Cargo Library 2 DOT_hazardous_materials</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cargo_synonym</t>
+          <t>cargo_dot_hazad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2864,25 +3080,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>cargo_synonym.source_id</t>
+          <t>cargo_dot_hazad.source_id</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1438</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
+          <t>Cargo Library 2 DOT_hazardous_materials</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>cargo_hazard_data</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2892,25 +3108,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>cargo_hazard_data.source_id</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>311</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>cargo_hazard_data</t>
+          <t>cleaning_process</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2920,25 +3136,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>cargo_hazard_data.source_id</t>
+          <t>cleaning_process.source_id</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>310</v>
+        <v>184468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>cargo_un_number</t>
+          <t>cargo_property_values</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2948,81 +3164,81 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cargo_un_number.source_id</t>
+          <t>cargo_property_values.source_id</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>235</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unknown - Products CHEM - 1996</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cargo_property_values</t>
+          <t>procedure_template_steps</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cargo_property_values.source_id</t>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>596</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unknown - Products CHEM - 1996</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cargo_chemical</t>
+          <t>procedure_template_instruction</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>cargo_chemical.source_id</t>
+          <t>procedure_template_instruction.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>313</v>
+        <v>567</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crude Oil Basic Properties</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>crude_oil_property_values</t>
+          <t>cargo_chemical</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3032,25 +3248,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>crude_oil_property_values.source_id</t>
+          <t>cargo_chemical.source_id</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>409</v>
+        <v>555</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crude Oil Basic Properties</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>crude_oil</t>
+          <t>cargo_family_group</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3060,11 +3276,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>crude_oil.source_id</t>
+          <t>cargo_family_group.source_id</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>138</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49">
@@ -3073,12 +3289,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crude Oil Assay and Operational Properties</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>crude_oil_property_values</t>
+          <t>procedure_templates</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3088,11 +3304,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>crude_oil_property_values.source_id</t>
+          <t>procedure_templates.source_id</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>5710</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50">
@@ -3101,30 +3317,1066 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>cargo_synonym</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>cargo_synonym.source_id</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>23</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ORIGIN ONLY</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Crude Oil Basic Properties</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Crude Oil Basic Properties</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>25</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Crude Oil Assay and Operational Properties</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5710</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>25</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Crude Oil Assay and Operational Properties</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>crude_oil</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>crude_oil.source_id</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F55" t="n">
         <v>426</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>26</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cleaning_process</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>cleaning_process.source_id</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>26</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>26</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>26</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym.source_id</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>26</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ORIGIN ONLY</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>26</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>procedure_template_instruction</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>procedure_template_instruction.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>26</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>procedure_templates</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>26</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>26</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>procedure_note</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>procedure_note.source_id</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>27</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>cleaning_process</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>cleaning_process.source_id</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>27</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>27</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>27</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>27</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HM Tank Cleaning Guide By Energy Institute</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>procedure_templates</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>28</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>cleaning_process</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>cleaning_process.source_id</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>28</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility.source_id</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>28</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>28</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>28</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>procedure_templates</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>28</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym.source_id</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>28</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ORIGIN ONLY</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>29</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>cleaning_process</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>cleaning_process.source_id</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>29</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>29</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>29</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>procedure_templates</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>29</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>30</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>cleaning_process</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>cleaning_process.source_id</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>30</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility.source_id</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>30</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>procedure_template_steps.procedure_templates_id -&gt; procedure_templates.id -&gt; procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>30</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>procedure_templates</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>procedure_templates.source_id</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>30</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>30</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3135,11 +4387,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -3215,7 +4467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cargo_coating</t>
+          <t>cargo_dot_hazad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3225,25 +4477,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cargo_coating.source_id</t>
+          <t>cargo_dot_hazad.source_id</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cargo Library 2 DOT_hazardous_materials</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cargo_dot_hazad</t>
+          <t>cargo_family_group</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3253,25 +4505,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cargo_dot_hazad.source_id</t>
+          <t>cargo_family_group.source_id</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Cargo Library 2 DOT_hazardous_materials</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3594</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cargo_family_group</t>
+          <t>cargo_gas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3281,95 +4533,123 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cargo_family_group.source_id</t>
+          <t>cargo_gas.source_id</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>cargo_gas_property_values</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cargo_gas_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>cargo_hazard_data</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>cargo_hazard_data.source_id</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Cargo Library 2 DOT_hazardous_materials
 USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cargo_operational_requirement</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INDIRECT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>via operational_requirement.source_id (cargo_operational_requirement.operational_requirement_id)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>IBC Code</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" t="n">
-        <v>2453</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>cargo_operational_requirement</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>via operational_requirement.source_id (cargo_operational_requirement.operational_requirement_id)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>IBC Code</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>cargo_property_values</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>cargo_property_values.source_id</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Dr Verweys Tank Cleaning Guide Pdf Book
 Lars Stole Birkeland — Chemical Cargo specifications - 2002
@@ -3379,45 +4659,17 @@
 Unknown - Products CHEM - 1996</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="n">
-        <v>49690</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cargo_reactive_group</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cargo_reactive_group.source_id</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" t="n">
-        <v>1586</v>
+        <v>48012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cargo_required_cleanliness</t>
+          <t>cargo_reactive_group</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3427,19 +4679,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cargo_required_cleanliness.source_id</t>
+          <t>cargo_reactive_group.source_id</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="11">
@@ -3501,497 +4753,526 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>839</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>changelog</t>
+          <t>cleaning_process</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NOT SCOPED</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>audit trail, references a source but is not owned by one</t>
+          <t>cleaning_process.source_id</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BP Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide - Oil
+Dr Verweys Tank Cleaning Guide Pdf Book
+Drew Ameroid Tank Cleaning Guide (TCG)
+HM Tank Cleaning Guide By Energy Institute
+Miracle Tank Cleaning Guide
+Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>327115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cleaning_process</t>
+          <t>cleaning_process_step</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>INDIRECT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cleaning_process.source_id</t>
+          <t>via cleaning_process.source_id (cleaning_process_step.cleaning_process_id)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Dr Verweys Tank Cleaning Guide
+Miracle Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>689020</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>compatibility</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>compatibility.source_id</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>compatibility_exception</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>compatibility_exception.source_id</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>USCG CHRIS Chemical Data Guide</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>crude_oil</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>crude_oil.source_id</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide
+Crude Oil Assay and Operational Properties
+Crude Oil Basic Properties
+Dr Verweys Tank Cleaning Guide - Oil
+HM Tank Cleaning Guide By Energy Institute
+Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>crude_oil_compatibility.source_id</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide - Oil
+Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>crude_oil_property_values.source_id</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide
+Crude Oil Assay and Operational Properties
+Crude Oil Basic Properties
+Dr Verweys Tank Cleaning Guide - Oil
+HM Tank Cleaning Guide By Energy Institute
+Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6327</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>crude_oil_synonym.source_id</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>field_definitions</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NOT SCOPED</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>shared property vocabulary across all sources</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>master_cargo_chemical_group_details</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>via reactive_groups.source_id (master_cargo_chemical_group_details.group_code)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>operational_requirement</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>operational_requirement.source_id</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>IBC Code</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>procedure_note</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>procedure_note.source_id</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>procedure_template_instruction</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>via procedure_templates.source_id (procedure_template_instruction.procedure_templates_id)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book
+Shell Tank Cleaning Guide 2016.pdf</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>procedure_template_note</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NOT SCOPED</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>no source linkage</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>procedure_template_requirement</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NOT SCOPED</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>no source linkage</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>procedure_template_steps</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INDIRECT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>via procedure_templates.source_id (procedure_template_steps.procedure_templates_id)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>BP Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide - Oil
 Dr Verweys Tank Cleaning Guide Pdf Book
 Drew Ameroid Tank Cleaning Guide (TCG)
-Miracle Tank Cleaning Guide</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>306712</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cleaning_process_step</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INDIRECT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>via cleaning_process.source_id (cleaning_process_step.cleaning_process_id)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Dr Verweys Tank Cleaning Guide
-Miracle Tank Cleaning Guide</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>600867</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cleanliness_standards</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>cleanliness_standards.source_id</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>coating_company</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NOT SCOPED</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>reference data, not source-scoped</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>coating_system</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NOT SCOPED</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>reference data, not source-scoped</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>compatibility</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>compatibility.source_id</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>compatibility_exception</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>compatibility_exception.source_id</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>USCG CHRIS Chemical Data Guide</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>crude_oil</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>crude_oil.source_id</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Crude Oil Assay and Operational Properties
-Crude Oil Basic Properties</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>crude_oil_property_values</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>crude_oil_property_values.source_id</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Crude Oil Assay and Operational Properties
-Crude Oil Basic Properties</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6119</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>field_definitions</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NOT SCOPED</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>shared property vocabulary across all sources</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>marine_chemical_use</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NOT SCOPED</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>links marine_chemicals to cargo; scope comes from the parent</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>marine_chemicals</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>marine_chemicals.source_id</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>master_cargo_chemical_group_details</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INDIRECT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>via reactive_groups.source_id (master_cargo_chemical_group_details.group_code)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>operational_requirement</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>operational_requirement.source_id</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>IBC Code</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>procedure_template_instruction</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>INDIRECT</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>via procedure_templates.source_id (procedure_template_instruction.procedure_templates_id)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Dr Verweys Tank Cleaning Guide Pdf Book</t>
+HM Tank Cleaning Guide By Energy Institute
+Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>567</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>procedure_template_steps</t>
+          <t>procedure_templates</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INDIRECT</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>via procedure_templates.source_id (procedure_template_steps.procedure_templates_id)</t>
+          <t>procedure_templates.source_id</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide
+          <t>BP Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide
+Dr Verweys Tank Cleaning Guide - Oil
 Dr Verweys Tank Cleaning Guide Pdf Book
-Drew Ameroid Tank Cleaning Guide (TCG)</t>
+Drew Ameroid Tank Cleaning Guide (TCG)
+HM Tank Cleaning Guide By Energy Institute
+Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>1437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>procedure_templates</t>
+          <t>reactive_groups</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4001,109 +5282,85 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>procedure_templates.source_id</t>
+          <t>reactive_groups.source_id</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Dr Verweys Tank Cleaning Guide
-Dr Verweys Tank Cleaning Guide Pdf Book
-Drew Ameroid Tank Cleaning Guide (TCG)</t>
+          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>338</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>reactive_groups</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>NOT SCOPED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>reactive_groups.source_id</t>
+          <t>the source registry itself</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Cargo Library 3 TABLE OF CHEMICAL CARGO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>synonyms</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NOT SCOPED</t>
+          <t>ORIGIN ONLY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>the source registry itself</t>
+          <t>shared name vocabulary; source_id = who introduced the text. Per-use source is on cargo_synonym / crude_oil_synonym.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dr Verweys Tank Cleaning Guide Pdf Book
+Lars Stole Birkeland — Chemical Cargo specifications - 2002
+Miracle Tank Cleaning Guide
+Shell Tank Cleaning Guide 2016.pdf
+Shell White Oil Tank Cleaning Guide
+Sittigs Handbook of Toxic &amp; Hazardous Chemicals
+USCG Chemical Data Guide For Bulk Shipment By Water [7th Edition 1990]_reviewed</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NOT SCOPED</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>shared name vocabulary; the link row cargo_synonym carries the source</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>11878</v>
+        <v>11975</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F33"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4158,7 +5415,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py</t>
+          <t>chemical/master_loader.py</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4183,7 +5440,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>cargo_compatibility.py</t>
+          <t>chemical/cargo_compatibility.py</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4205,9 +5462,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>dot_hmt_extract.py
-dot_hazmat_symbol_loader.py
-cargo_dot_hazad_loader.py</t>
+          <t>chemical/dot_hmt_extract.py
+chemical/dot_hazmat_symbol_loader.py
+chemical/cargo_dot_hazad_loader.py</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4229,8 +5486,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>proceduretemplate.py
-verwey_cleaning.py</t>
+          <t>chemical/proceduretemplate.py
+chemical/verwey_cleaning.py</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4255,8 +5512,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>proceduretemplate.py
-verwey_cleaning.py</t>
+          <t>chemical/proceduretemplate.py
+chemical/verwey_cleaning.py</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4281,10 +5538,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>verwey_pdf_book.py
-verwey_pdf_book_procedures.py
-verwey_pdf_book_families.py
-verwey_pdf_book_matrix.py</t>
+          <t>chemical/verwey_pdf_book.py
+chemical/verwey_pdf_book_procedures.py
+chemical/verwey_pdf_book_families.py
+chemical/verwey_pdf_book_matrix.py</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4296,7 +5553,8 @@
 cleaning_process
 procedure_template_instruction
 procedure_template_steps
-procedure_templates</t>
+procedure_templates
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4313,10 +5571,10 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>verwey_pdf_book.py
-verwey_pdf_book_procedures.py
-verwey_pdf_book_families.py
-verwey_pdf_book_matrix.py</t>
+          <t>chemical/verwey_pdf_book.py
+chemical/verwey_pdf_book_procedures.py
+chemical/verwey_pdf_book_families.py
+chemical/verwey_pdf_book_matrix.py</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4328,7 +5586,8 @@
 cleaning_process
 procedure_template_instruction
 procedure_template_steps
-procedure_templates</t>
+procedure_templates
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4345,10 +5604,10 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>verwey_pdf_book.py
-verwey_pdf_book_procedures.py
-verwey_pdf_book_families.py
-verwey_pdf_book_matrix.py</t>
+          <t>chemical/verwey_pdf_book.py
+chemical/verwey_pdf_book_procedures.py
+chemical/verwey_pdf_book_families.py
+chemical/verwey_pdf_book_matrix.py</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4360,7 +5619,8 @@
 cleaning_process
 procedure_template_instruction
 procedure_template_steps
-procedure_templates</t>
+procedure_templates
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4377,7 +5637,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>drew_ameroid.py</t>
+          <t>chemical/drew_ameroid.py</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4401,8 +5661,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py
-cargo_operational_requirement.py</t>
+          <t>chemical/master_loader.py
+chemical/cargo_operational_requirement.py</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4426,8 +5686,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py
-cargo_operational_requirement.py</t>
+          <t>chemical/master_loader.py
+chemical/cargo_operational_requirement.py</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4451,7 +5711,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py</t>
+          <t>chemical/master_loader.py</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4459,7 +5719,8 @@
           <t>cargo_chemical
 cargo_property_values
 cargo_synonym
-cargo_un_number</t>
+cargo_un_number
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4476,7 +5737,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py</t>
+          <t>chemical/master_loader.py</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4486,7 +5747,8 @@
 cargo_synonym
 cargo_un_number
 cleaning_process
-cleaning_process_step</t>
+cleaning_process_step
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4503,9 +5765,9 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>cargo_compatibility.py
-reactive_group.py
-link_cargo_reactive_groups.py</t>
+          <t>chemical/cargo_compatibility.py
+chemical/reactive_group.py
+chemical/link_cargo_reactive_groups.py</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4527,9 +5789,9 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>cargo_compatibility.py
-reactive_group.py
-link_cargo_reactive_groups.py</t>
+          <t>chemical/cargo_compatibility.py
+chemical/reactive_group.py
+chemical/link_cargo_reactive_groups.py</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4551,14 +5813,15 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>sittig_handbook.py</t>
+          <t>chemical/sittig_handbook.py</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>cargo_chemical
 cargo_property_values
-cargo_synonym</t>
+cargo_synonym
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4575,7 +5838,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>compatibility_exception_loader.py</t>
+          <t>chemical/compatibility_exception_loader.py</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4597,7 +5860,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py</t>
+          <t>chemical/master_loader.py</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4606,7 +5869,8 @@
 cargo_hazard_data
 cargo_property_values
 cargo_synonym
-cargo_un_number</t>
+cargo_un_number
+synonyms</t>
         </is>
       </c>
     </row>
@@ -4623,7 +5887,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>master_loader.py</t>
+          <t>chemical/master_loader.py</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
